--- a/out_data/not_ring.xlsx
+++ b/out_data/not_ring.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gyoumu04\Documents\prog\python\area_calc\out_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1AB2F3-E212-4A29-85F6-7257B40B3863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8622A3-FFF0-46E8-A663-8C0F9754E399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0C2161C4-17E1-43E4-980E-86C42D7A1B4A}"/>
   </bookViews>
   <sheets>
-    <sheet name="操業範囲" sheetId="1" r:id="rId1"/>
-    <sheet name="メッシュ根拠" sheetId="2" r:id="rId2"/>
+    <sheet name="操業範囲" sheetId="2" r:id="rId1"/>
+    <sheet name="メッシュ根拠" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">メッシュ根拠!$A:$D</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">操業範囲!$A:$D</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,8 +40,101 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>メッシュ位置</t>
+    <rPh sb="4" eb="6">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>面積(m2)</t>
+    <rPh sb="0" eb="2">
+      <t>メンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>漁場の重み</t>
+    <rPh sb="0" eb="2">
+      <t>ギョバ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>面積×重み</t>
+    <rPh sb="0" eb="2">
+      <t>メンセキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(m2)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>磯判定</t>
+    <rPh sb="0" eb="1">
+      <t>イソ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合計</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内外判定</t>
+    <rPh sb="0" eb="2">
+      <t>ナイガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cad戻し</t>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0.000000_ "/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -63,7 +160,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -71,15 +168,136 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -414,21 +632,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374898E2-E67A-4B1D-9FC3-03F9615B5023}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2EFD2F-CADC-499B-9318-7BED2620255F}">
+  <dimension ref="C1:M4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="20.375" style="11" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" style="11" customWidth="1"/>
+    <col min="8" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="19.25" style="1" customWidth="1"/>
+    <col min="11" max="14" width="9" style="1"/>
+    <col min="15" max="15" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.25" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="3:13" x14ac:dyDescent="0.4">
+      <c r="C2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="3:13" x14ac:dyDescent="0.4">
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.4">
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;P / &amp;N ページ</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2EFD2F-CADC-499B-9318-7BED2620255F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374898E2-E67A-4B1D-9FC3-03F9615B5023}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="4" width="15.625" customWidth="1"/>
+  </cols>
   <sheetData/>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>